--- a/Dataset_1/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_1/4_Integration_results/Stats_table_final.xlsx
@@ -47,19 +47,13 @@
     <t xml:space="preserve">Recall genes</t>
   </si>
   <si>
-    <t xml:space="preserve">Tot.associations...intersection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perc.sig.lm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perc.sig.Spearman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perc.unique.sig.lm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perc.unique.sig.Spearman</t>
+    <t xml:space="preserve">Tot associations - intersection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc sig Spearman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc unique sig Spearman</t>
   </si>
   <si>
     <t xml:space="preserve">expected_perc</t>
@@ -68,61 +62,67 @@
     <t xml:space="preserve">odds_ratio</t>
   </si>
   <si>
-    <t xml:space="preserve">Sign of inters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All DM up (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM ∩ DE DM up (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M ∩ DE vs All DM up (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All DM down (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM ∩ DE DM down (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M ∩ DE vs All DM down (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypo-up (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypo-down (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyper-up (p)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyper-down (p)</t>
+    <t xml:space="preserve">pvalue_quadrants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pvalue_quadrants_BH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign of inters (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All DM up (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM ∩ DE DM up (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M ∩ DE vs All DM up (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All DM down (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM ∩ DE DM down (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M ∩ DE vs All DM down (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypo-up (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypo-down (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyper-up (padj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyper-down (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">meth Spear (rho)</t>
   </si>
   <si>
-    <t xml:space="preserve">meth Spear (p)</t>
+    <t xml:space="preserve">meth Spear (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">Multi DM genes</t>
   </si>
   <si>
-    <t xml:space="preserve">Multi DM ∩ DE (p)</t>
+    <t xml:space="preserve">Multi DM ∩ DE (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">sites vs |log2FC| (rho)</t>
   </si>
   <si>
-    <t xml:space="preserve">sites vs |log2FC| (p)</t>
+    <t xml:space="preserve">sites vs |log2FC| (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">sites vs log2FC (rho)</t>
   </si>
   <si>
-    <t xml:space="preserve">sites vs log2FC (p)</t>
+    <t xml:space="preserve">sites vs log2FC (padj)</t>
   </si>
 </sst>
 </file>
@@ -476,19 +476,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="C2" t="n">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
-        <v>231</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
@@ -496,19 +496,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -516,19 +516,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.508196721311475</v>
+        <v>0.487179487179487</v>
       </c>
       <c r="C4" t="n">
-        <v>0.450819672131148</v>
+        <v>0.423076923076923</v>
       </c>
       <c r="D4" t="n">
-        <v>0.411764705882353</v>
+        <v>0.363636363636364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.29004329004329</v>
+        <v>0.256756756756757</v>
       </c>
     </row>
     <row r="5">
@@ -536,19 +536,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -556,19 +556,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0077909022367429</v>
+        <v>0.00477506911284242</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00691128424227193</v>
+        <v>0.00414677054536316</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000879617994470973</v>
+        <v>0.000502638853983413</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0018848957024378</v>
+        <v>0.00100527770796683</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00841920080422217</v>
+        <v>0.00477506911284242</v>
       </c>
     </row>
     <row r="7">
@@ -576,19 +576,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
-        <v>16</v>
-      </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -621,9 +621,7 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
+      <c r="D9"/>
       <c r="E9" t="n">
         <v>0</v>
       </c>
@@ -636,17 +634,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>83.0769230769231</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10"/>
+        <v>87.3015873015873</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>76.4705882352941</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>71.0843373493976</v>
       </c>
     </row>
     <row r="11">
@@ -654,17 +654,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4.90909090909091</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11"/>
+        <v>6.875</v>
+      </c>
+      <c r="D11" t="e">
+        <v>#NUM!</v>
+      </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.45833333333333</v>
       </c>
     </row>
     <row r="12">
@@ -672,19 +674,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>84.4036697247706</v>
+        <v>0.000000030137695171547</v>
       </c>
       <c r="C12" t="n">
-        <v>86.5384615384615</v>
+        <v>0.000000000488083654330736</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>0.001953125</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>0.0245208740234375</v>
       </c>
       <c r="F12" t="n">
-        <v>71.2230215827338</v>
+        <v>0.0000772797053916459</v>
       </c>
     </row>
     <row r="13">
@@ -692,19 +694,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>5.41176470588235</v>
+        <v>0.0000000753442379288675</v>
       </c>
       <c r="C13" t="n">
-        <v>6.42857142857143</v>
-      </c>
-      <c r="D13" t="e">
-        <v>#NUM!</v>
+        <v>0.00000000244041827165368</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.00244140625</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>0.0245208740234375</v>
       </c>
       <c r="F13" t="n">
-        <v>2.475</v>
+        <v>0.000128799508986077</v>
       </c>
     </row>
     <row r="14">
@@ -712,19 +714,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>0.000000000181675083831975</v>
+        <v>0.0000038888686777618</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000000101032046006104</v>
+        <v>0.000498139951358724</v>
       </c>
       <c r="D14" t="n">
-        <v>0.041485598057698</v>
+        <v>0.883928571428571</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0163228702539388</v>
+        <v>0.472543041101429</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00000272646752185517</v>
+        <v>0.00485177428464727</v>
       </c>
     </row>
     <row r="15">
@@ -732,19 +734,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0000000000023771972868561</v>
+        <v>0.00000293041090249409</v>
       </c>
       <c r="C15" t="n">
-        <v>0.000000000131279188761044</v>
+        <v>0.0000235467657342789</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0116083620633733</v>
+        <v>0.588176457858568</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0297975965935796</v>
+        <v>0.558728744843535</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00000000079852312239711</v>
+        <v>0.000777764165533464</v>
       </c>
     </row>
     <row r="16">
@@ -752,19 +754,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>0.000000000129222173774693</v>
+        <v>0.0000038888686777618</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0000000000396968473826326</v>
+        <v>0.000000942465330786333</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000643658540175879</v>
+        <v>0.139791597489381</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0134965543336971</v>
+        <v>0.334196172013003</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00000250713636726065</v>
+        <v>0.00121772647273904</v>
       </c>
     </row>
     <row r="17">
@@ -772,19 +774,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>0.000305106484434684</v>
+        <v>0.0538345844136345</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0082843700696387</v>
+        <v>0.37029790145376</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.363768115942029</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0000120319960139122</v>
+        <v>0.0730821635521323</v>
       </c>
     </row>
     <row r="18">
@@ -792,19 +794,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>0.999999999999825</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.999999999989037</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.993063152432524</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.999999999884454</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -812,19 +814,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>0.999999999973113</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.999999999992583</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.995632015326908</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.999999003458182</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -832,19 +834,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>0.999969352932958</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.99864264665004</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.889855072463768</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.99999833291748</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -932,19 +934,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0854314922515623</v>
+        <v>-0.287520378971977</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.119907807548257</v>
+        <v>-0.221120984278879</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.427272727272727</v>
+        <v>-0.535714285714286</v>
       </c>
       <c r="E25" t="n">
-        <v>0.084911439178423</v>
+        <v>0.0429338790741092</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0362725366243725</v>
+        <v>-0.1927177369501</v>
       </c>
     </row>
     <row r="26">
@@ -952,19 +954,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>0.412287296638922</v>
+        <v>0.0869667158568022</v>
       </c>
       <c r="C26" t="n">
-        <v>0.25976789249299</v>
+        <v>0.328258090046122</v>
       </c>
       <c r="D26" t="n">
-        <v>0.19262499772471</v>
+        <v>0.883928571428571</v>
       </c>
       <c r="E26" t="n">
-        <v>0.673684172741887</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.689189796093572</v>
+        <v>0.307082888629452</v>
       </c>
     </row>
     <row r="27">
@@ -972,19 +974,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -992,19 +994,19 @@
         <v>32</v>
       </c>
       <c r="B28" t="n">
-        <v>0.636365646219887</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.248075928320896</v>
+        <v>0.328258090046122</v>
       </c>
       <c r="D28" t="n">
-        <v>0.669117647058824</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.897854720056385</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.824583700305377</v>
+        <v>0.764855218489335</v>
       </c>
     </row>
     <row r="29">
@@ -1012,19 +1014,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.153114515129657</v>
+        <v>-0.0490032381705998</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0225151729753521</v>
+        <v>0.145316204945283</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.074535599249993</v>
+        <v>-0.158113883008419</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.428446535248488</v>
+        <v>-0.499312714451762</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.093892422335922</v>
+        <v>-0.100210703231666</v>
       </c>
     </row>
     <row r="30">
@@ -1032,19 +1034,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="n">
-        <v>0.14065924837772</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.833169288300693</v>
+        <v>0.53483945646787</v>
       </c>
       <c r="D30" t="n">
-        <v>0.827585596577687</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0257670480514789</v>
+        <v>0.435738384369142</v>
       </c>
       <c r="F30" t="n">
-        <v>0.299621104445006</v>
+        <v>0.764855218489335</v>
       </c>
     </row>
     <row r="31">
@@ -1052,19 +1054,19 @@
         <v>35</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.0758256883273388</v>
+        <v>-0.00474224885521934</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0484069465768818</v>
+        <v>0.195425241133312</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.074535599249993</v>
+        <v>-0.158113883008419</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.183619943677923</v>
+        <v>-0.408528584551442</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0854224788468729</v>
+        <v>-0.0983199352461629</v>
       </c>
     </row>
     <row r="32">
@@ -1072,19 +1074,19 @@
         <v>36</v>
       </c>
       <c r="B32" t="n">
-        <v>0.467613443079996</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.650494687093594</v>
+        <v>0.37029790145376</v>
       </c>
       <c r="D32" t="n">
-        <v>0.827585596577687</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.359248221588985</v>
+        <v>0.489655542796698</v>
       </c>
       <c r="F32" t="n">
-        <v>0.345519101940073</v>
+        <v>0.764855218489335</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_1/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_1/4_Integration_results/Stats_table_final.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">metric</t>
   </si>
@@ -50,10 +50,22 @@
     <t xml:space="preserve">Tot associations - intersection</t>
   </si>
   <si>
-    <t xml:space="preserve">Perc sig Spearman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perc unique sig Spearman</t>
+    <t xml:space="preserve">Perc sig CpG-gene Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc sig genes Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc unique sig Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc sig CpG-gene eQTM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc sig genes eQTM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc unique sig eQTM</t>
   </si>
   <si>
     <t xml:space="preserve">expected_perc</t>
@@ -77,7 +89,7 @@
     <t xml:space="preserve">DM ∩ DE DM up (padj)</t>
   </si>
   <si>
-    <t xml:space="preserve">M ∩ DE vs All DM up (padj)</t>
+    <t xml:space="preserve">DM ∩ DE vs All DM up (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">All DM down (padj)</t>
@@ -86,7 +98,7 @@
     <t xml:space="preserve">DM ∩ DE DM down (padj)</t>
   </si>
   <si>
-    <t xml:space="preserve">M ∩ DE vs All DM down (padj)</t>
+    <t xml:space="preserve">DM ∩ DE vs All DM down (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">Hypo-up (padj)</t>
@@ -621,7 +633,9 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9"/>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
@@ -634,19 +648,17 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>83.0769230769231</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>87.3015873015873</v>
-      </c>
-      <c r="D10" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D10"/>
       <c r="E10" t="n">
-        <v>76.4705882352941</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>71.0843373493976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -654,19 +666,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>4.90909090909091</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>6.875</v>
-      </c>
-      <c r="D11" t="e">
-        <v>#NUM!</v>
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.45833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -674,19 +686,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>0.000000030137695171547</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.000000000488083654330736</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001953125</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0245208740234375</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0000772797053916459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -694,19 +706,17 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0000000753442379288675</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00000000244041827165368</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.00244140625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D13"/>
       <c r="E13" t="n">
-        <v>0.0245208740234375</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.000128799508986077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -714,19 +724,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0000038888686777618</v>
+        <v>92.8571428571429</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000498139951358724</v>
+        <v>92.1052631578947</v>
       </c>
       <c r="D14" t="n">
-        <v>0.883928571428571</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>0.472543041101429</v>
+        <v>71.4285714285714</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00485177428464727</v>
+        <v>84.6153846153846</v>
       </c>
     </row>
     <row r="15">
@@ -734,19 +744,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00000293041090249409</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0000235467657342789</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.588176457858568</v>
+        <v>11.6666666666667</v>
+      </c>
+      <c r="D15" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E15" t="n">
-        <v>0.558728744843535</v>
+        <v>2.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.000777764165533464</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
@@ -754,19 +764,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0000038888686777618</v>
+        <v>0.000000002815795596689</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000000942465330786333</v>
+        <v>0.0000000333893694914879</v>
       </c>
       <c r="D16" t="n">
-        <v>0.139791597489381</v>
+        <v>0.03125</v>
       </c>
       <c r="E16" t="n">
-        <v>0.334196172013003</v>
+        <v>0.2265625</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00121772647273904</v>
+        <v>0.00000714963061909659</v>
       </c>
     </row>
     <row r="17">
@@ -774,19 +784,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0538345844136345</v>
+        <v>0.000000014078977983445</v>
       </c>
       <c r="C17" t="n">
-        <v>0.37029790145376</v>
+        <v>0.0000000834734237287198</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.0390625</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.2265625</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0730821635521323</v>
+        <v>0.0000119160510318277</v>
       </c>
     </row>
     <row r="18">
@@ -794,19 +804,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0.0000038888686777618</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.000498139951358724</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0.901237527641636</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.472543041101429</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.00485177428464727</v>
       </c>
     </row>
     <row r="19">
@@ -814,19 +824,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0.0000038888686777618</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.000000942465330786333</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.139791597489381</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.334196172013003</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.00121772647273904</v>
       </c>
     </row>
     <row r="20">
@@ -834,19 +844,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0.00000293041090249409</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.0000235467657342789</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.588176457858568</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.558728744843535</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.000777764165533464</v>
       </c>
     </row>
     <row r="21">
@@ -854,10 +864,10 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0.0538345844136345</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0.43201421836272</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -866,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.0730821635521323</v>
       </c>
     </row>
     <row r="22">
@@ -934,19 +944,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.287520378971977</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.221120984278879</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.535714285714286</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0429338790741092</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1927177369501</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -954,19 +964,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0869667158568022</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.328258090046122</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.883928571428571</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.307082888629452</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -974,19 +984,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -997,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.328258090046122</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -1006,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.764855218489335</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1014,19 +1024,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.0490032381705998</v>
+        <v>-0.342378816063027</v>
       </c>
       <c r="C29" t="n">
-        <v>0.145316204945283</v>
+        <v>-0.170788770053476</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.158113883008419</v>
+        <v>-0.4</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.499312714451762</v>
+        <v>-0.251501515001784</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.100210703231666</v>
+        <v>-0.291561788751234</v>
       </c>
     </row>
     <row r="30">
@@ -1034,19 +1044,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0.107842361017408</v>
       </c>
       <c r="C30" t="n">
-        <v>0.53483945646787</v>
+        <v>0.638505301443118</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.435738384369142</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.764855218489335</v>
+        <v>0.227157750341307</v>
       </c>
     </row>
     <row r="31">
@@ -1054,19 +1064,19 @@
         <v>35</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.00474224885521934</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>0.195425241133312</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.158113883008419</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.408528584551442</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0983199352461629</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1077,15 +1087,95 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.37029790145376</v>
+        <v>0.410322612557652</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.764855218489335</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.0490032381705998</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.145316204945283</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.158113883008419</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.499312714451762</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.100210703231666</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.611245093106137</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.435738384369142</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.764855218489335</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.00474224885521934</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.195425241133312</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.158113883008419</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.408528584551442</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.0983199352461629</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.43201421836272</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.489655542796698</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F36" t="n">
         <v>0.764855218489335</v>
       </c>
     </row>

--- a/Dataset_1/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_1/4_Integration_results/Stats_table_final.xlsx
@@ -568,19 +568,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00477506911284242</v>
+        <v>0.00476608553869309</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00414677054536316</v>
+        <v>0.004138969020444</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000502638853983413</v>
+        <v>0.000501693214599273</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00100527770796683</v>
+        <v>0.00100338642919855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00477506911284242</v>
+        <v>0.00476608553869309</v>
       </c>
     </row>
     <row r="7">
@@ -804,19 +804,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0000038888686777618</v>
+        <v>0.00000355326533919672</v>
       </c>
       <c r="C18" t="n">
-        <v>0.000498139951358724</v>
+        <v>0.000464392094727034</v>
       </c>
       <c r="D18" t="n">
-        <v>0.901237527641636</v>
+        <v>0.892848483173247</v>
       </c>
       <c r="E18" t="n">
-        <v>0.472543041101429</v>
+        <v>0.464844480131948</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00485177428464727</v>
+        <v>0.00453317867739901</v>
       </c>
     </row>
     <row r="19">
@@ -824,19 +824,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0000038888686777618</v>
+        <v>0.00000355326533919672</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000000942465330786333</v>
+        <v>0.000000959731648928046</v>
       </c>
       <c r="D19" t="n">
-        <v>0.139791597489381</v>
+        <v>0.140233606764425</v>
       </c>
       <c r="E19" t="n">
-        <v>0.334196172013003</v>
+        <v>0.335610576284992</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00121772647273904</v>
+        <v>0.00123616286381568</v>
       </c>
     </row>
     <row r="20">
@@ -844,19 +844,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>0.00000293041090249409</v>
+        <v>0.00000315974257154784</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0000235467657342789</v>
+        <v>0.0000250917030022579</v>
       </c>
       <c r="D20" t="n">
-        <v>0.588176457858568</v>
+        <v>0.593749848190987</v>
       </c>
       <c r="E20" t="n">
-        <v>0.558728744843535</v>
+        <v>0.56454093324686</v>
       </c>
       <c r="F20" t="n">
-        <v>0.000777764165533464</v>
+        <v>0.000826613332473205</v>
       </c>
     </row>
     <row r="21">

--- a/Dataset_1/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_1/4_Integration_results/Stats_table_final.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">metric</t>
   </si>
@@ -99,18 +99,6 @@
   </si>
   <si>
     <t xml:space="preserve">DM ∩ DE vs All DM down (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypo-up (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypo-down (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyper-up (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyper-down (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">meth Spear (rho)</t>
@@ -804,19 +792,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00000355326533919672</v>
+        <v>0.00000260572791541093</v>
       </c>
       <c r="C18" t="n">
-        <v>0.000464392094727034</v>
+        <v>0.000340554202799825</v>
       </c>
       <c r="D18" t="n">
-        <v>0.892848483173247</v>
+        <v>0.654755554327048</v>
       </c>
       <c r="E18" t="n">
-        <v>0.464844480131948</v>
+        <v>0.340885952096762</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00453317867739901</v>
+        <v>0.00332433103009261</v>
       </c>
     </row>
     <row r="19">
@@ -824,19 +812,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>0.00000355326533919672</v>
+        <v>0.00000260572791541093</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000000959731648928046</v>
+        <v>0.0000007038032092139</v>
       </c>
       <c r="D19" t="n">
-        <v>0.140233606764425</v>
+        <v>0.102837978293912</v>
       </c>
       <c r="E19" t="n">
-        <v>0.335610576284992</v>
+        <v>0.246114422608994</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00123616286381568</v>
+        <v>0.000906519433464835</v>
       </c>
     </row>
     <row r="20">
@@ -844,19 +832,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>0.00000315974257154784</v>
+        <v>0.00000231714455246842</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0000250917030022579</v>
+        <v>0.0000184005822016558</v>
       </c>
       <c r="D20" t="n">
-        <v>0.593749848190987</v>
+        <v>0.435416555340057</v>
       </c>
       <c r="E20" t="n">
-        <v>0.56454093324686</v>
+        <v>0.413996684381031</v>
       </c>
       <c r="F20" t="n">
-        <v>0.000826613332473205</v>
+        <v>0.00060618311048035</v>
       </c>
     </row>
     <row r="21">
@@ -864,10 +852,10 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0538345844136345</v>
+        <v>0.0394786952366653</v>
       </c>
       <c r="C21" t="n">
-        <v>0.43201421836272</v>
+        <v>0.316810426799328</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -876,7 +864,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0730821635521323</v>
+        <v>0.053593586604897</v>
       </c>
     </row>
     <row r="22">
@@ -884,10 +872,10 @@
         <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0.999999982872045</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.999999989332212</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -896,7 +884,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.999990125969684</v>
       </c>
     </row>
     <row r="23">
@@ -904,10 +892,10 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0.999999982872045</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.999999989332212</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -916,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.999990125969684</v>
       </c>
     </row>
     <row r="24">
@@ -924,19 +912,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0.999999982872045</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.999999989332212</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.87032967032967</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.999990125969684</v>
       </c>
     </row>
     <row r="25">
@@ -944,19 +932,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>-0.342378816063027</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>-0.170788770053476</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>-0.251501515001784</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>-0.291561788751234</v>
       </c>
     </row>
     <row r="26">
@@ -964,19 +952,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0.0790843980794323</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0.468237221058286</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.87032967032967</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.166582350250292</v>
       </c>
     </row>
     <row r="27">
@@ -984,19 +972,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1004,10 +992,10 @@
         <v>32</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.863165905631659</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.300903249208945</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -1016,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0.560893826892179</v>
       </c>
     </row>
     <row r="29">
@@ -1024,19 +1012,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.342378816063027</v>
+        <v>-0.0490032381705998</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.170788770053476</v>
+        <v>0.145316204945283</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4</v>
+        <v>-0.158113883008419</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.251501515001784</v>
+        <v>-0.499312714451762</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.291561788751234</v>
+        <v>-0.100210703231666</v>
       </c>
     </row>
     <row r="30">
@@ -1044,19 +1032,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="n">
-        <v>0.107842361017408</v>
+        <v>0.999999982872045</v>
       </c>
       <c r="C30" t="n">
-        <v>0.638505301443118</v>
+        <v>0.448246401611167</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.319541481870704</v>
       </c>
       <c r="F30" t="n">
-        <v>0.227157750341307</v>
+        <v>0.560893826892179</v>
       </c>
     </row>
     <row r="31">
@@ -1064,19 +1052,19 @@
         <v>35</v>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>-0.00474224885521934</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>0.195425241133312</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>-0.158113883008419</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>-0.408528584551442</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>-0.0983199352461629</v>
       </c>
     </row>
     <row r="32">
@@ -1084,99 +1072,19 @@
         <v>36</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0.999999982872045</v>
       </c>
       <c r="C32" t="n">
-        <v>0.410322612557652</v>
+        <v>0.316810426799328</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.359080731384245</v>
       </c>
       <c r="F32" t="n">
-        <v>0.764855218489335</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="n">
-        <v>-0.0490032381705998</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.145316204945283</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-0.158113883008419</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-0.499312714451762</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-0.100210703231666</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.611245093106137</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.435738384369142</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.764855218489335</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" t="n">
-        <v>-0.00474224885521934</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.195425241133312</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-0.158113883008419</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-0.408528584551442</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-0.0983199352461629</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.43201421836272</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.489655542796698</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.764855218489335</v>
+        <v>0.560893826892179</v>
       </c>
     </row>
   </sheetData>
